--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -817,12 +817,7 @@
         <v>81033564</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Belägg granskat av validerare.</t>
-        </is>
+        <v>110077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519787.0432679179</v>
+        <v>519787</v>
       </c>
       <c r="R3" t="n">
-        <v>6434418.935621653</v>
+        <v>6434419</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -899,19 +894,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -817,7 +817,7 @@
         <v>81033564</v>
       </c>
       <c r="B3" t="n">
-        <v>110077</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>519787</v>
       </c>
       <c r="R8" t="n">
-        <v>6434419</v>
+        <v>6434420</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1485,6 +1485,11 @@
       <c r="AP8" t="inlineStr">
         <is>
           <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>OGN 321148</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1432,7 +1432,7 @@
         <v>519787</v>
       </c>
       <c r="R8" t="n">
-        <v>6434420</v>
+        <v>6434419</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>519787</v>
       </c>
       <c r="R10" t="n">
-        <v>6434419</v>
+        <v>6434420</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1717,6 +1717,11 @@
       <c r="AP10" t="inlineStr">
         <is>
           <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>OHN 321382</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>519787</v>
       </c>
       <c r="R10" t="n">
-        <v>6434420</v>
+        <v>6434419</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16037943</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -923,6 +933,11 @@
           <t>Projekt Östergötland Flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118599007</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339084</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339544</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339571</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339627</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1513,6 +1548,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89458093</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,6 +1655,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339492</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81033564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1848,6 +1898,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16038001</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1950,6 +2005,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339629</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2052,6 +2112,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339653</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2149,6 +2214,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4099689</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2268,6 +2338,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73818620</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2378,6 +2453,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339471</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,8 +2568,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>89458093</v>
       </c>
       <c r="B8" t="n">
-        <v>109896</v>
+        <v>109952</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>81033564</v>
       </c>
       <c r="B10" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>89458093</v>
       </c>
       <c r="B8" t="n">
-        <v>109952</v>
+        <v>109979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>81033564</v>
       </c>
       <c r="B10" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126339492</v>
+        <v>89458093</v>
       </c>
       <c r="B8" t="n">
-        <v>109815</v>
+        <v>109984</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,22 +1451,26 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N Axsjön, Ög</t>
+          <t>Malexanders socken, Axsjön 500 m N, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519771</v>
+        <v>519787</v>
       </c>
       <c r="R8" t="n">
-        <v>6434436</v>
+        <v>6434419</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,12 +1494,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,30 +1512,54 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>OGN 321148</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126339492</t>
+          <t>https://artportalen.se/Sighting/89458093</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16038001</v>
+        <v>126339492</v>
       </c>
       <c r="B9" t="n">
-        <v>102225</v>
+        <v>109815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,49 +1567,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>220204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Axsjön 450 m N, Ärtvägen O, Ög</t>
+          <t>N Axsjön, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519774</v>
+        <v>519771</v>
       </c>
       <c r="R9" t="n">
-        <v>6434425</v>
+        <v>6434436</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,12 +1625,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,33 +1639,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16038001</t>
+          <t>https://artportalen.se/Sighting/126339492</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126339629</v>
+        <v>81033564</v>
       </c>
       <c r="B10" t="n">
-        <v>102225</v>
+        <v>110247</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,41 +1674,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221223</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N Axsjön, Ög</t>
+          <t>Malexanders socken, Axsjön 450 m N, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519731</v>
+        <v>519787</v>
       </c>
       <c r="R10" t="n">
-        <v>6434397</v>
+        <v>6434419</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,12 +1736,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,30 +1754,45 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Oskarshamn-Herbarium OHN</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>OHN 321382</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Carin Gondesen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126339629</t>
+          <t>https://artportalen.se/Sighting/81033564</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126339653</v>
+        <v>16038001</v>
       </c>
       <c r="B11" t="n">
-        <v>102419</v>
+        <v>102225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,38 +1800,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221317</v>
+        <v>221223</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pollich</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N Axsjön, Ög</t>
+          <t>Axsjön 450 m N, Ärtvägen O, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519687</v>
+        <v>519774</v>
       </c>
       <c r="R11" t="n">
-        <v>6434402</v>
+        <v>6434425</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,12 +1869,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2014-06-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,34 +1883,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126339653</t>
+          <t>https://artportalen.se/Sighting/16038001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4099689</v>
+        <v>126339629</v>
       </c>
       <c r="B12" t="n">
-        <v>103647</v>
+        <v>102225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,37 +1917,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221978</v>
+        <v>221223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypericum montanum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ärtvägen. Malexander, Ög</t>
+          <t>N Axsjön, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519718</v>
+        <v>519731</v>
       </c>
       <c r="R12" t="n">
-        <v>6434418</v>
+        <v>6434397</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,12 +1975,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-08-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-08-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,33 +1989,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Simon Jakobsson</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Simon Jakobsson</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4099689</t>
+          <t>https://artportalen.se/Sighting/126339629</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73818620</v>
+        <v>126339653</v>
       </c>
       <c r="B13" t="n">
-        <v>103647</v>
+        <v>102419</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,50 +2024,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221978</v>
+        <v>221317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypericum montanum</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Axsjön 450 m N, Ärtvägen O, Ög</t>
+          <t>N Axsjön, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519774</v>
+        <v>519687</v>
       </c>
       <c r="R13" t="n">
-        <v>6434425</v>
+        <v>6434402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,17 +2082,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-06-23</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-06-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Återfynd på känd lokal. Endast enstaka plantor noterade, varav en blommande.</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,24 +2103,24 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rikard Anderberg, Maya Edlund</t>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73818620</t>
+          <t>https://artportalen.se/Sighting/126339653</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126339471</v>
+        <v>4099689</v>
       </c>
       <c r="B14" t="n">
         <v>103647</v>
@@ -2113,32 +2148,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>N Axsjön, Ög</t>
+          <t>Ärtvägen. Malexander, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519771</v>
+        <v>519718</v>
       </c>
       <c r="R14" t="n">
-        <v>6434436</v>
+        <v>6434418</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,12 +2185,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2010-08-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2010-08-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,31 +2199,30 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Simon Jakobsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Simon Jakobsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126339471</t>
+          <t>https://artportalen.se/Sighting/4099689</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126339558</v>
+        <v>73818620</v>
       </c>
       <c r="B15" t="n">
         <v>103647</v>
@@ -2230,27 +2252,31 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Axsjön, Ög</t>
+          <t>Axsjön 450 m N, Ärtvägen O, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519792</v>
+        <v>519774</v>
       </c>
       <c r="R15" t="n">
-        <v>6434453</v>
+        <v>6434425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2277,12 +2303,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2012-06-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2012-06-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Återfynd på känd lokal. Endast enstaka plantor noterade, varav en blommande.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,16 +2329,246 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Rikard Anderberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+          <t>Rikard Anderberg, Maya Edlund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73818620</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126339471</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Axsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>519771</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6434436</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boxholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Malexander</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126339471</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126339558</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>N Axsjön, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>519792</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6434453</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boxholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Malexander</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein, Claes Svedlindh, Ebba Wadstein</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126339558</t>
         </is>
@@ -2329,6 +2590,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>89458093</v>
       </c>
       <c r="B8" t="n">
-        <v>109984</v>
+        <v>109986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>81033564</v>
       </c>
       <c r="B10" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>89458093</v>
       </c>
       <c r="B8" t="n">
-        <v>109986</v>
+        <v>110009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>81033564</v>
       </c>
       <c r="B10" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 42147-2025 artfynd.xlsx
+++ b/artfynd/A 42147-2025 artfynd.xlsx
@@ -1666,7 +1666,7 @@
         <v>81033564</v>
       </c>
       <c r="B10" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
